--- a/整理后数据/2501/银行卡2001_2501.xlsx
+++ b/整理后数据/2501/银行卡2001_2501.xlsx
@@ -540,7 +540,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>示例银行B2001</t>
+          <t>示例银行B</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>示例银行B2001</t>
+          <t>示例银行B</t>
         </is>
       </c>
     </row>
